--- a/daily_matches/job_matches_2026-07-13.xlsx
+++ b/daily_matches/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,12 +468,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Architect, Forward Deployed Engineer (Cogentiq)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Fractal Analytics</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -482,126 +482,651 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>16.7</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Docker, Kubernetes, CI/CD, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Prompt Engineering, S3, EC2, Redshift, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f263d55b51a9b05</t>
+          <t>https://www.indeed.com/viewjob?jk=622d3a3e3c903762</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data and Analytics Engineer</t>
+          <t>Reliability Engineer, Battery Module</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Digital Strategy LLC</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sparks, NV, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, S3, CI/CD, Git, Snowflake, Databricks, PySpark, Power BI, Python, SQL</t>
+          <t>RAG, TensorFlow, PyTorch, Docker, Kubernetes, Apache Airflow, CI/CD, Git, Tableau, Power BI</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd127ae8715c196f</t>
+          <t>https://www.indeed.com/viewjob?jk=3af907c177dd5fdb</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer</t>
+          <t>AI, Content Intelligence Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Pinecone, Prompt Engineering, TensorFlow, PyTorch, Keras, Git, Python, R</t>
+          <t>Generative AI, RAG, FAISS, Pinecone, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89bbe544c85b0240</t>
+          <t>https://www.indeed.com/viewjob?jk=d1c8de23682a4a0d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Production AI Engineer Owning High-Scale Cloud Infrastructure</t>
+          <t>Senior AI &amp; Cloud Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Check Point Software Technologies</t>
+          <t>Publicis Groupe</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Prompt Engineering, Data Lake, MLflow, CI/CD, GitHub Actions, Git, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e3b212b4def3f9f</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>AI Architect</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Gemini, Copilot, TensorFlow, PyTorch, Keras, OpenCV, NoSQL, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1914a3917afdf4e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26c2fa1d45c9055b</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (Big Data)</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2025-10-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d8e19f0fb16bc7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Gemini, Git, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f85d5258e31e33e</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, Gemini, Git, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=98e26081d0ff7940</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Robots &amp; Pencils</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Data Lake, Kinesis, CI/CD, Kafka, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e79c7f1ba1f3eb0a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Kimball Midwest</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Columbus, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Copilot, Synapse, Dataflow, Databricks, PySpark, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2dd6388cdeebf986</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, CI/CD, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ea4e80f245f26c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-25</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93a262e17ee30703</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>AI Technical Architect</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Gemini, TensorFlow, PyTorch, Keras, OpenCV, NoSQL, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2025-12-17</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=037ee83ae1b82c61</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Software Engineer, Front-End</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Cisco</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Milpitas, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
         <v>10</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Jenkins, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=523e21481735f5a7</t>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7aa2882444b9b452</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Senior Network Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-11</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a43ff272be49d7a6</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, Databricks, Hadoop, Python, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81752facbba9d16c</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Data Scientist II</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Git, PySpark, Tableau, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cab40aeb52a009f5</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>10</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, BigQuery, Git, BigQuery, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2025-12-10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7f7d87e5ca07b8cd</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-13.xlsx
+++ b/daily_matches/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Aurora Innovation</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>11.1</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Copilot, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, NoSQL, SQL, R</t>
+          <t>Data Scientist, RAG, S3, Glue, Redshift, BigQuery, Data Lake, Kinesis, Apache Airflow, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3004d47870448a1</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Cloud Engineer</t>
+          <t>Engineering Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Smart Apply Test Company</t>
+          <t>Citi</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Prompt Engineering, Data Lake, MLflow, Databricks, Python, R, Scala</t>
+          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,42 +531,462 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45f4cc37f4bedee9</t>
+          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>Software Engineer II - Enterprise AI Products</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Travelers</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>17.8</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Senior Cyber AI Operations Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>VIVA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e4a409c671f30f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
           <t>Software Engineer</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Smart Apply Test Company</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Publicis Groupe</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Westminster, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Sr. Marketing Data Analyst</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>WebstaurantStore</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Lititz, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=470c0b95102d6675</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Tata Consultancy Services (TCS)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Johns Creek, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Gemini, Copilot, BigQuery, BigQuery, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6314c157aedefc2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Databricks Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>VIVA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Clifton, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Databricks, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Data Integration Operations Engineerr</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Northeastern University</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
         <v>10</v>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, Databricks, Hadoop, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d697f334d121ec3</t>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AI Engineer 4A</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ad2c2238c437c9b</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AI Engineer 4A</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Genpact</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d7716603984c4de8</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>DevOps Engineer - Docker &amp; CI/CD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Optimal Inc.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Warren, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a3e59540ee80fbd5</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>fixed-term project engagement|Backend Developer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>株式会社天地人</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Docker, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=760a817428d56361</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Wilmington, DE, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>10</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8f53c0b9664a12a6</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-13.xlsx
+++ b/daily_matches/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (Data Engineering and Infrastructure)</t>
+          <t>Generative AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Aurora Innovation</t>
+          <t>Afficiency</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Glue, Redshift, BigQuery, Data Lake, Kinesis, Apache Airflow, Terraform</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, MLflow, FastAPI, Docker</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b8b74c1db36b82</t>
+          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Engineering Architect</t>
+          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Citi</t>
+          <t>Molina Healthcare</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.8</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Prompt Engineering, Docker, Kubernetes, CI/CD, Terraform, Git, PostgreSQL, MongoDB</t>
+          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Keras, CI/CD, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e831741c10ec9a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer II - Enterprise AI Products</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.8</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Kubernetes, AKS, CI/CD, Jenkins, GitHub Actions, Terraform, Git, MongoDB</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dcac0248b7373d4</t>
+          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Cyber AI Operations Engineer</t>
+          <t>Threat Detection Engineer – Security Operations</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>ID.me</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, LLaMA, Mistral, TensorFlow, PyTorch, Docker, Kubernetes, CI/CD, Terraform</t>
+          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4a409c671f30f0</t>
+          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior System Software Engineer for Cloud – GeForce NOW</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NVIDIA</t>
+          <t>Vytalize Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python, R, Java</t>
+          <t>LangChain, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,102 +636,102 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d6d30e78e6f4c6e</t>
+          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Engineer, Software</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Publicis Groupe</t>
+          <t>Verint Systems Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Westminster, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Git, Databricks, Hadoop, Python, SQL, R, Java</t>
+          <t>Prompt Engineering, Docker, Kubernetes, AKS, Jenkins, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41b78df5b95306be</t>
+          <t>https://www.indeed.com/viewjob?jk=1834f6658eb4ad57</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Marketing Data Analyst</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>WebstaurantStore</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lititz, PA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, Data Lake, BigQuery, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=470c0b95102d6675</t>
+          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Backend Python Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>NextAmp LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Johns Creek, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Copilot, BigQuery, BigQuery, Python, SQL, R, Java</t>
+          <t>FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6314c157aedefc2</t>
+          <t>https://www.indeed.com/viewjob?jk=936d018d49bfbe89</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Engineer</t>
+          <t>Senior Solutions Architect - AI and Emerging Technologies</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>Micron Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Clifton, NJ, US USA</t>
+          <t>Boise, ID, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>13.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Databricks, Hadoop, Python, SQL, R, Java, Scala, Optimization</t>
+          <t>Generative AI, RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=009aa09bd21a9217</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7ac273e7455b75</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Integration Operations Engineerr</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Northeastern University</t>
+          <t>C.H. Robinson</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wood Dale, IL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>13.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, CI/CD, Snowflake, Databricks, Python, SQL, R, Optimization</t>
+          <t>AI Engineer, RAG, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=748fc639b3268939</t>
+          <t>https://www.indeed.com/viewjob?jk=b321a37f5bde5878</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer 4A</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Veho</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,19 +846,19 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad2c2238c437c9b</t>
+          <t>https://www.indeed.com/viewjob?jk=78a7a8efdc400062</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Engineer 4A</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Veho</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -867,11 +867,11 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, Git, Python, SQL, R, Java</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7716603984c4de8</t>
+          <t>https://www.indeed.com/viewjob?jk=54163520c7c8e41d</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>DevOps Engineer - Docker &amp; CI/CD</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Optimal Inc.</t>
+          <t>Veho</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a3e59540ee80fbd5</t>
+          <t>https://www.indeed.com/viewjob?jk=9bd50f847afc4581</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fixed-term project engagement|Backend Developer</t>
+          <t>Senior Machine Learning Operations Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>株式会社天地人</t>
+          <t>Veho</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Docker, CI/CD, Kafka, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,42 +951,812 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760a817428d56361</t>
+          <t>https://www.indeed.com/viewjob?jk=da3534cacc529490</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Science Senior Associate- Card Data &amp; Analytics team</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>SEI Investments</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Oaks, PA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Tableau, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df83019ac3e233df</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>DevOps / Site Reliability Engineer (SRE)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NextAmp LLC</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fe7dee874f8154a9</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Engineer - TDM, Python, Julia</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Julia, Scala</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8e526e10cb76b337</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Payments - Software Engineer 3</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>eBay</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Git, Hadoop, MongoDB, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bad61c33c290069f</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=11948dc7785339a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Senior Applied ML Engineer</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Middleton, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=578333b2a6d767d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1f75e78463b4621</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=04631de77572d89f</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Paradigm</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Middleton, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=481cd1f193ba2a11</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Applied Machine Learning Engineer I - Advanced Engineering &amp; Technology</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Milwaukee Tool</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Brookfield, WI, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, SQL, R, Optimization, Bayesian</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08170d654a61bcb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Associate Engineer, Technology I</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>AbbVie</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>North Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Athena, FastAPI, Snowflake, Power BI, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=21c1c1179fdbb54e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer (Python + Vue.js)</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>NextAmp LLC</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>S3, FastAPI, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=220374c3ef2b87ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>DevOps Engineer T2—(Ansible / Terraform / GitLab) | Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AiGeniusGov</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9500f7731301ac51</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-05-12</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-05-06</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>AI Research Scientist</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Austin Powder</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef7b25c385b04207</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Healthcare Data Scientist</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Novi, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=748e7f05db9fb94d</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>DevOps Engineer T3 Senior — (Terraform / Ansible / Multi-Cloud) | Cloud Infrastructure</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>AiGeniusGov</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
         <v>10</v>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Prompt Engineering, Git, Hadoop, Tableau, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8f53c0b9664a12a6</t>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a9a0ac85b4652cb3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Senior Machine Learning Scientist - Agentic Experience</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>10</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=df4cb28b39a329ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Data Engineer - &amp; Modeler Informatica</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Software Engineer III</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>C.H. Robinson</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>10</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, Copilot, Docker, Git, MongoDB, Python, SQL, R</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e20c78e12ef06f8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Analyst, Applied AI Solutions</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>10</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d98792fe418ece09</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Machine Learning Scientist II</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Expedia Group</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>10</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3532957e52c02e61</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-13.xlsx
+++ b/daily_matches/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generative AI Engineer</t>
+          <t>Databricks Solution Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Afficiency</t>
+          <t>Bounteous</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>22.2</v>
+        <v>20</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, MLflow, FastAPI, Docker</t>
+          <t>Data Scientist, RAG, S3, Kinesis, MLflow, CI/CD, Terraform, Git, Snowflake, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be5a298b53e539ed</t>
+          <t>https://www.indeed.com/viewjob?jk=95200cc7178deeb2</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Scientist - GenAI/Agentic AI - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Molina Healthcare</t>
+          <t>GroundWork Renewables, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Albuquerque, NM, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Data Scientist, RAG, LLaMA, TensorFlow, PyTorch, Keras, CI/CD, Snowflake, Databricks</t>
+          <t>RAG, Copilot, FastAPI, Docker, Apache Airflow, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34b1a1a8543d5bde</t>
+          <t>https://www.indeed.com/viewjob?jk=d2bead5227e03d14</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Senior Analytics Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>FirstDay Foundation</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>16.7</v>
+        <v>15.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845986ee9c384d0c</t>
+          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Threat Detection Engineer – Security Operations</t>
+          <t>Architect of Data Architecture</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ID.me</t>
+          <t>Empower</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>14.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>LangChain, RAG, LLaMA, Gemini, Prompt Engineering, Data Lake, Kubernetes, CI/CD, Terraform, Git</t>
+          <t>Generative AI, RAG, Redshift, Kinesis, Kubernetes, CI/CD, Snowflake, Redshift, Kafka, R</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb9bc641ca30ce01</t>
+          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Analytics Data Engineer, Cat Digital</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Vytalize Health</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>LangChain, S3, EC2, Kinesis, Docker, Kubernetes, CI/CD, GitHub Actions, Terraform, Git</t>
+          <t>RAG, S3, EC2, Apache Airflow, CI/CD, Git, Snowflake, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,19 +636,19 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=439c58ad35a8bb78</t>
+          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr. Engineer, Software</t>
+          <t>Marketing Technology Strategist</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Verint Systems Inc.</t>
+          <t>Phase2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -657,11 +657,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Docker, Kubernetes, AKS, Jenkins, Git, PostgreSQL, MongoDB, NoSQL, SQL</t>
+          <t>RAG, Copilot, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,59 +671,59 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1834f6658eb4ad57</t>
+          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>ClassWallet</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, Copilot, Kubernetes, CI/CD, Git, Snowflake, MongoDB, NoSQL</t>
+          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, MongoDB, SQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c90454ed63602f69</t>
+          <t>https://www.indeed.com/viewjob?jk=42da2a0fcfb874bc</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Backend Python Developer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>Scigon</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, CI/CD, Git, Kafka, PostgreSQL, MySQL, Python, SQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=936d018d49bfbe89</t>
+          <t>https://www.indeed.com/viewjob?jk=39740d9a53d791d8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Solutions Architect - AI and Emerging Technologies</t>
+          <t>Software Engineer, AI Engineering and Enablement</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Micron Technology</t>
+          <t>Bristol Myers Squibb</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boise, ID, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Cortex, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>AI Engineer, RAG, S3, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7ac273e7455b75</t>
+          <t>https://www.indeed.com/viewjob?jk=7b781ccfbe89edeb</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. IT Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>C.H. Robinson</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Wood Dale, IL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, CI/CD, Git, Kafka, MongoDB, NoSQL, SQL, R, Java</t>
+          <t>RAG, Kafka, Hadoop, MySQL, MongoDB, Cassandra, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b321a37f5bde5878</t>
+          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Pre-Sales Solutions Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Veho</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78a7a8efdc400062</t>
+          <t>https://www.indeed.com/viewjob?jk=0037bc04d435d2f1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Software Engineer - X Data</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Veho</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, BigQuery, BigQuery, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54163520c7c8e41d</t>
+          <t>https://www.indeed.com/viewjob?jk=b1d6746fe0c3f27c</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Senior Support Engineer(B2Bi)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Veho</t>
+          <t>Precisely</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Cassandra, NoSQL, SQL, R, Java</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bd50f847afc4581</t>
+          <t>https://www.indeed.com/viewjob?jk=e038e65cdc67c1c9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Operations Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Veho</t>
+          <t>CESO, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
+          <t>RAG, S3, Data Lake, AKS, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da3534cacc529490</t>
+          <t>https://www.indeed.com/viewjob?jk=2357627a980cd7f4</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SEI Investments</t>
+          <t>CESO, Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Oaks, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, AKS, CI/CD, Jenkins, Terraform, Git, Tableau, SQL</t>
+          <t>RAG, S3, Data Lake, AKS, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df83019ac3e233df</t>
+          <t>https://www.indeed.com/viewjob?jk=74b887cacf8f0667</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>DevOps / Site Reliability Engineer (SRE)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>NextAmp LLC</t>
+          <t>CESO, Inc.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Akron, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, S3, Data Lake, AKS, Git, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe7dee874f8154a9</t>
+          <t>https://www.indeed.com/viewjob?jk=0214d33dd28834f8</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer - TDM, Python, Julia</t>
+          <t>Conversational AI Engineer - Google/GECX &amp; Code Agents</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>TTEC Digital</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Julia, Scala</t>
+          <t>AI Engineer, RAG, Gemini, Prompt Engineering, BigQuery, CI/CD, Git, BigQuery, Python, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e526e10cb76b337</t>
+          <t>https://www.indeed.com/viewjob?jk=1a271868c59f62fd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Payments - Software Engineer 3</t>
+          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>RAG, Git, Hadoop, MongoDB, Cassandra, NoSQL, SQL, R, Java, Scala</t>
+          <t>BigQuery, Kubernetes, Terraform, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bad61c33c290069f</t>
+          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Generative AI, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11948dc7785339a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a519e3b2e75f251b</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Applied ML Engineer</t>
+          <t>Software Engineer - Data</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Hugging Face, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, R, Scala</t>
+          <t>RAG, Data Lake, Kubernetes, PostgreSQL, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=578333b2a6d767d4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcf606c20df8fd9d</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Consumer Subscriptions</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d1f75e78463b4621</t>
+          <t>https://www.indeed.com/viewjob?jk=6574a38a7cede23a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Data Engineer - Consumer Subscriptions</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04631de77572d89f</t>
+          <t>https://www.indeed.com/viewjob?jk=6ba851adfa684389</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>AI Engineer – Enterprise, Data &amp; AI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Zoox</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Foster City, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Terraform, Git, Python, R, Scala, Optimization</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=481cd1f193ba2a11</t>
+          <t>https://www.indeed.com/viewjob?jk=d336a8922f853892</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer I - Advanced Engineering &amp; Technology</t>
+          <t>Sr. Data Engineer, Ops Decision Systems</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Milwaukee Tool</t>
+          <t>Rivian</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Brookfield, WI, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Python, SQL, R, Optimization, Bayesian</t>
+          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Python, SQL, R, Optimization</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08170d654a61bcb7</t>
+          <t>https://www.indeed.com/viewjob?jk=eead309102a709c2</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Associate Engineer, Technology I</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Atmosphere TV</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>North Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RAG, Prompt Engineering, Athena, FastAPI, Snowflake, Power BI, Python, SQL, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Python, SQL, R, Optimization, Bayesian, A/B Testing</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,427 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c1c1179fdbb54e</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Full Stack Engineer (Python + Vue.js)</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>NextAmp LLC</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>S3, FastAPI, Git, PostgreSQL, MySQL, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=220374c3ef2b87ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>DevOps Engineer T2—(Ansible / Terraform / GitLab) | Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>AiGeniusGov</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9500f7731301ac51</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-05-12</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=14d4be214d89c9f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, Kafka, MongoDB, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-05-06</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3fd7b858f4e17691</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>AI Research Scientist</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Austin Powder</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>OH, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, MLflow, CI/CD, Git, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7b25c385b04207</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Healthcare Data Scientist</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Novi, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, Hadoop, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=748e7f05db9fb94d</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>DevOps Engineer T3 Senior — (Terraform / Ansible / Multi-Cloud) | Cloud Infrastructure</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>AiGeniusGov</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>10</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a9a0ac85b4652cb3</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Senior Machine Learning Scientist - Agentic Experience</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>10</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=df4cb28b39a329ba</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Data Engineer - &amp; Modeler Informatica</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>10</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Data Lake, Git, Snowflake, Databricks, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=aebf504e442ce2f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>C.H. Robinson</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Copilot, Docker, Git, MongoDB, Python, SQL, R</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>2026-06-02</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e20c78e12ef06f8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Analyst, Applied AI Solutions</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>10</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>RAG, Gemini, Copilot, Git, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d98792fe418ece09</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Machine Learning Scientist II</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Expedia Group</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>10</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, LangChain, RAG, LLaMA, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3532957e52c02e61</t>
+          <t>https://www.indeed.com/viewjob?jk=85323e77d4638f70</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-13.xlsx
+++ b/daily_matches/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,17 +468,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Databricks Solution Architect</t>
+          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bounteous</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -486,7 +486,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Kinesis, MLflow, CI/CD, Terraform, Git, Snowflake, Databricks</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95200cc7178deeb2</t>
+          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer (AI)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GroundWork Renewables, Inc.</t>
+          <t>Invovia</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Albuquerque, NM, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>20</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, FastAPI, Docker, Apache Airflow, CI/CD, Git, PostgreSQL, MySQL, NoSQL</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, CI/CD</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2bead5227e03d14</t>
+          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Analytics Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FirstDay Foundation</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>20</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Prompt Engineering, Git, Snowflake, Databricks, Tableau, Power BI, Python</t>
+          <t>AI Engineer, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d797cade2cc30f67</t>
+          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Architect of Data Architecture</t>
+          <t>Sr. Machine Learning Platform Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Empower</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Greenwood Village, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Redshift, Kinesis, Kubernetes, CI/CD, Snowflake, Redshift, Kafka, R</t>
+          <t>Data Scientist, RAG, BigQuery, FastAPI, Docker, Kubernetes, Terraform, Git, Snowflake, BigQuery</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a69b442d48a997e</t>
+          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Analytics Data Engineer, Cat Digital</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Apache Airflow, CI/CD, Git, Snowflake, Power BI, Python, SQL</t>
+          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ba56e26d2f7d66e</t>
+          <t>https://www.indeed.com/viewjob?jk=0de590782059756c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marketing Technology Strategist</t>
+          <t>Senior Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Phase2</t>
+          <t>C2FO</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>14.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Redshift, BigQuery, Git, Snowflake, BigQuery, Redshift, Python, SQL</t>
+          <t>Data Scientist, Glue, Redshift, Docker, Kubernetes, Redshift, Kafka, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08cde2c4527579db</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>ClassWallet</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, Git, Kafka, PostgreSQL, MySQL, MongoDB, SQL</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, BigQuery, BigQuery, Python</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=42da2a0fcfb874bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6bb665d6403cd93b</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Scigon</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Git, Python, R, Java</t>
+          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39740d9a53d791d8</t>
+          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Software Engineer, AI Engineering and Enablement</t>
+          <t>Network Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Bristol Myers Squibb</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, S3, CI/CD, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b781ccfbe89edeb</t>
+          <t>https://www.indeed.com/viewjob?jk=bd021ef938d1ce24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. IT Data Engineer</t>
+          <t>Sr. Developer - Software Engineering</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Kafka, Hadoop, MySQL, MongoDB, Cassandra, Python, SQL, R, Java</t>
+          <t>RAG, Copilot, S3, EC2, Glue, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d0debfb86cec6f81</t>
+          <t>https://www.indeed.com/viewjob?jk=902ddb871e38ae79</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Pre-Sales Solutions Engineer</t>
+          <t>Software Engineer, Data Infrastructure</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>The Voleon Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0037bc04d435d2f1</t>
+          <t>https://www.indeed.com/viewjob?jk=77c0df21ad2fb4c0</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Software Engineer - X Data</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,15 +863,15 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Kafka, NoSQL, Python, SQL, R, Java, Scala</t>
+          <t>Synapse, Docker, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,59 +881,59 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1d6746fe0c3f27c</t>
+          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Support Engineer(B2Bi)</t>
+          <t>Senior Data Scientist (55_2026.2)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Precisely</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Copilot, Docker, Kubernetes, Cassandra, NoSQL, SQL, R, Java</t>
+          <t>Data Scientist, RAG, S3, Redshift, Data Lake, Snowflake, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e038e65cdc67c1c9</t>
+          <t>https://www.indeed.com/viewjob?jk=429f2392d3780cae</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, AKS, Git, Python, SQL, R, Java, Scala</t>
+          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2357627a980cd7f4</t>
+          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, AKS, Git, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74b887cacf8f0667</t>
+          <t>https://www.indeed.com/viewjob?jk=a896f90b98a816b1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CESO, Inc.</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Akron, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RAG, S3, Data Lake, AKS, Git, Python, SQL, R, Java, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0214d33dd28834f8</t>
+          <t>https://www.indeed.com/viewjob?jk=0e22a443c81ec156</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Conversational AI Engineer - Google/GECX &amp; Code Agents</t>
+          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>TTEC Digital</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Gemini, Prompt Engineering, BigQuery, CI/CD, Git, BigQuery, Python, R</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a271868c59f62fd</t>
+          <t>https://www.indeed.com/viewjob?jk=64d5dcd728c6801b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Enterprise, Data &amp; AI</t>
+          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Paradigm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Middleton, WI, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>BigQuery, Kubernetes, Terraform, Snowflake, Databricks, BigQuery, Python, SQL, R, Scala</t>
+          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=303390f40d7bb17a</t>
+          <t>https://www.indeed.com/viewjob?jk=bd0fd1292263a0f5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Scientist</t>
+          <t>Pre-Sales Solutions Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, Cortex, CI/CD, Git, Snowflake, Python, SQL, R, Scala</t>
+          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a519e3b2e75f251b</t>
+          <t>https://www.indeed.com/viewjob?jk=4948b8847b375ce0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Software Engineer - Data</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RAG, Data Lake, Kubernetes, PostgreSQL, Python, SQL, R, Java, Scala</t>
+          <t>AI Engineer, RAG, Prompt Engineering, S3, FastAPI, Kubernetes, Python, R, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcf606c20df8fd9d</t>
+          <t>https://www.indeed.com/viewjob?jk=40c1e1dc88c11d9a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Consumer Subscriptions</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, Kafka, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6574a38a7cede23a</t>
+          <t>https://www.indeed.com/viewjob?jk=cca6f8353cab27ec</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Consumer Subscriptions</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RAG, BigQuery, BigQuery, Tableau, Python, SQL, R, Optimization, A/B Testing</t>
+          <t>RAG, Docker, Kubernetes, Kafka, MongoDB, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ba851adfa684389</t>
+          <t>https://www.indeed.com/viewjob?jk=e658b01630c131ad</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI Engineer – Enterprise, Data &amp; AI</t>
+          <t>Senior Cyber Security Architect - Automation, Data Center &amp; Networking Security</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Zoox</t>
+          <t>Latitude AI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Foster City, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Prompt Engineering, Python, R, Optimization</t>
+          <t>RAG, CI/CD, Jenkins, Terraform, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,77 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d336a8922f853892</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Sr. Data Engineer, Ops Decision Systems</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Rivian</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>10</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Git, Databricks, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-07-09</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eead309102a709c2</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Senior Data Scientist</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Atmosphere TV</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>10</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, Git, Python, SQL, R, Optimization, Bayesian, A/B Testing</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=85323e77d4638f70</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3f69f3c3490863</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-07-13.xlsx
+++ b/daily_matches/job_matches_2026-07-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI) - Frisco, TX</t>
+          <t>AI Native Builder_EU</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, CI/CD</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8e491698172a68a</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea4fc6a360496ad</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer (AI)</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Invovia</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, Copilot, Pinecone, Prompt Engineering, Docker, CI/CD</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9389c7fce7ffb417</t>
+          <t>https://www.indeed.com/viewjob?jk=2df1f2e18d690c4a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>20</v>
+        <v>18.9</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, LLaMA, Gemini, Copilot, Prompt Engineering, TensorFlow, PyTorch, Docker, Kubernetes</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2545dd224fcef4a</t>
+          <t>https://www.indeed.com/viewjob?jk=d896c15ac717e14c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Machine Learning Platform Engineer</t>
+          <t>Forward Deployed Engineer-Specialist</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, BigQuery, FastAPI, Docker, Kubernetes, Terraform, Git, Snowflake, BigQuery</t>
+          <t>AI Engineer, RAG, Gemini, Copilot, Pinecone, Glue, MLflow, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40b7d898d0faad8</t>
+          <t>https://www.indeed.com/viewjob?jk=db4fe4e7c9a86b11</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Data Quality AI Intern (61_2026.3)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Affinity Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, TensorFlow, PyTorch, Git, Python</t>
+          <t>AI Engineer, Generative AI, Prompt Engineering, Redshift, BigQuery, Git, Snowflake, Databricks, BigQuery, Redshift</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0de590782059756c</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc7c811d1c4b67c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer I</t>
+          <t>Senior Data Scientist - AI Services and Platforms</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>C2FO</t>
+          <t>Highmark Health</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>14.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Glue, Redshift, Docker, Kubernetes, Redshift, Kafka, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, LLaMA, Gemini, AWS SageMaker, Azure ML, BigQuery, Git</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a710f918b88f2b</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7e18e976bb5293</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>Senior Data Management Professional - Data Engineering - Entities</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, LLaMA, Mistral, BigQuery, BigQuery, Python</t>
+          <t>RAG, S3, Glue, CI/CD, Git, Databricks, Kafka, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bb665d6403cd93b</t>
+          <t>https://www.indeed.com/viewjob?jk=44d437f6ae16eb4d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>AWS Severless Software Engineer III</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>NBME</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>FastAPI, Docker, Kubernetes, GitHub Actions, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>RAG, Copilot, S3, Glue, Athena, CI/CD, Terraform, Git, Python, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bc63eb13d50f0ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ce2dc4576aaa8a2e</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Network Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Lumen</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RAG, S3, EC2, Docker, Kubernetes, AKS, CI/CD, Terraform, Git, Python</t>
+          <t>Data Scientist, Generative AI, RAG, Git, Databricks, PySpark, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd021ef938d1ce24</t>
+          <t>https://www.indeed.com/viewjob?jk=59b50390528ec0d0</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Developer - Software Engineering</t>
+          <t>Senior Software Engineer, Core Systems &amp; Integrations</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LPL Financial</t>
+          <t>Omada Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, Copilot, S3, EC2, Glue, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, PostgreSQL, MySQL, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=902ddb871e38ae79</t>
+          <t>https://www.indeed.com/viewjob?jk=4508a1fd19332890</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer, Data Infrastructure</t>
+          <t>Machine Learning Engineer, Energy Hardware Engineering</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Voleon Group</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, Athena, BigQuery, Docker, Kubernetes, Snowflake, BigQuery, Python, R, Java</t>
+          <t>Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77c0df21ad2fb4c0</t>
+          <t>https://www.indeed.com/viewjob?jk=e9fabc10b29fae4c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist (Insurance Product)-Senior Associate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Synapse, Docker, Git, Snowflake, Databricks, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, Git, Tableau, Python, SQL, R, Scala, Optimization, Hypothesis Testing</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,67 +881,67 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=898a5660007f1525</t>
+          <t>https://www.indeed.com/viewjob?jk=a76b437b5c587569</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Scientist (55_2026.2)</t>
+          <t>AI Software Engineer - Greenwood Village, Colorado Office</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Affinity Solutions</t>
+          <t>Ulteig</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>12.2</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, S3, Redshift, Data Lake, Snowflake, Redshift, Python, SQL, R</t>
+          <t>AI Engineer, Generative AI, RAG, Copilot, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=429f2392d3780cae</t>
+          <t>https://www.indeed.com/viewjob?jk=7274b8978c8696ed</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Developer</t>
+          <t>Software Engineer II, MLOps</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, Jenkins, Git, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, RAG, AWS SageMaker, CI/CD, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a2f1102b97c2bd1</t>
+          <t>https://www.indeed.com/viewjob?jk=74ce0ce9ae06a2a9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
+          <t>Web Developer Security Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>CMT Services INC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>RAG, Copilot, S3, CI/CD, Git, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a896f90b98a816b1</t>
+          <t>https://www.indeed.com/viewjob?jk=0927c2d9913b6a8c</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
+          <t>Data Analytics and Research Analyst</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Serco</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>RAG, Redshift, Databricks, Redshift, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e22a443c81ec156</t>
+          <t>https://www.indeed.com/viewjob?jk=b25bdf252af26e0d</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Data Scientist, LangChain, RAG, Prompt Engineering, Docker, CI/CD, Python, SQL, R</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64d5dcd728c6801b</t>
+          <t>https://www.indeed.com/viewjob?jk=e227ca009286120f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - IBM App Connect Enterprise</t>
+          <t>Data Scientist II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Paradigm</t>
+          <t>CareSource</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Middleton, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, CI/CD, Jenkins, Git, Kafka, SQL, R, Java, Scala</t>
+          <t>Data Scientist, Snowflake, Databricks, Power BI, Python, SQL, R, Optimization, A/B Testing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,182 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd0fd1292263a0f5</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Pre-Sales Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Booz Allen Hamilton</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>RAG, Kubernetes, CI/CD, Jenkins, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4948b8847b375ce0</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Indianapolis, IN, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>10</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>AI Engineer, RAG, Prompt Engineering, S3, FastAPI, Kubernetes, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=40c1e1dc88c11d9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>ZoomInfo</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Bethesda, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>10</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Kafka, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cca6f8353cab27ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>ZoomInfo</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Waltham, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>10</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, Kafka, MongoDB, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e658b01630c131ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Senior Cyber Security Architect - Automation, Data Center &amp; Networking Security</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Latitude AI</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Pittsburgh, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>10</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Jenkins, Terraform, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-07-13</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3f69f3c3490863</t>
+          <t>https://www.indeed.com/viewjob?jk=3b359b418fb62a48</t>
         </is>
       </c>
     </row>
